--- a/data/trans_dic/P21D_4_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,54</t>
+          <t>0,25; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,3</t>
+          <t>0,15; 1,23</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,19; 1,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,98</t>
+          <t>0,08; 1,03</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,27</t>
+          <t>0,59; 3,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,25</t>
+          <t>0,52; 2,22</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,16</t>
+          <t>0,5; 3,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,79</t>
+          <t>0,32; 1,69</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,52</t>
+          <t>0,05; 0,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,31</t>
+          <t>0,49; 1,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,76</t>
+          <t>0,31; 0,81</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3690</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2689</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9347</t>
+          <t>0; 10837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8313</t>
+          <t>0; 9367</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>711; 6548</t>
+          <t>639; 6021</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>684; 6167</t>
+          <t>700; 5822</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6206</t>
+          <t>0; 6401</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5478</t>
+          <t>608; 5385</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>496; 8347</t>
+          <t>640; 8757</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6058</t>
+          <t>0; 5943</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1315; 7417</t>
+          <t>1337; 7712</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2346; 10447</t>
+          <t>2409; 10350</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1235</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>924; 5859</t>
+          <t>934; 5629</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1051; 6127</t>
+          <t>1105; 5777</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3120</t>
+          <t>0; 2810</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 946</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3595</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>676; 8695</t>
+          <t>796; 9442</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8255; 20783</t>
+          <t>7828; 21203</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9917; 24816</t>
+          <t>10170; 26447</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_4_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Edad-trans_dic.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,34</t>
+          <t>0,27; 2,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,23</t>
+          <t>0,15; 1,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,68</t>
+          <t>0,19; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,03</t>
+          <t>0,1; 1,22</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,4</t>
+          <t>0,53; 3,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,22</t>
+          <t>0,46; 2,07</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,04</t>
+          <t>0,69; 3,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,69</t>
+          <t>0,32; 1,76</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,57</t>
+          <t>0,07; 0,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,33</t>
+          <t>0,52; 1,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,81</t>
+          <t>0,36; 0,82</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2503</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 10837</t>
+          <t>0; 9878</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9367</t>
+          <t>0; 9365</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2664</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>639; 6021</t>
+          <t>798; 6325</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>700; 5822</t>
+          <t>819; 6546</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3188</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6401</t>
+          <t>0; 5671</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>608; 5385</t>
+          <t>672; 5484</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>640; 8757</t>
+          <t>695; 8056</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5495</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5943</t>
+          <t>0; 6859</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1337; 7712</t>
+          <t>1347; 7886</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2409; 10350</t>
+          <t>2362; 10572</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3231</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>934; 5629</t>
+          <t>1368; 7093</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1105; 5777</t>
+          <t>1184; 6584</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2810</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3595</t>
+          <t>0; 2938</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>17667</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>796; 9442</t>
+          <t>1149; 8584</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7828; 21203</t>
+          <t>8822; 21994</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10170; 26447</t>
+          <t>11739; 26607</t>
         </is>
       </c>
     </row>
